--- a/output/pdf_financials_xlsx/NL.xlsx
+++ b/output/pdf_financials_xlsx/NL.xlsx
@@ -5907,34 +5907,34 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.483285</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.204561</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.191906</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.191906</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.191906</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.191906</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.191906</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.191906</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.191906</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.191906</v>
       </c>
     </row>
     <row r="93">
@@ -7370,28 +7370,28 @@
         <v>0</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.196</v>
+        <v>0.101934</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0315</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0065</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0035</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0035</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.342065</v>
+        <v>0.338565</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.014105</v>
+        <v>0</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0.013305</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -9685,7 +9685,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10289,7 +10293,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -10798,7 +10806,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11768,7 +11780,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -12534,7 +12550,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -19236,7 +19256,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -20523,7 +20547,11 @@
           <t>Exploration and evaluation assets expenditure</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -21978,7 +22006,11 @@
           <t>Exploration and evaluation assets expenditure</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -23077,7 +23109,11 @@
           <t>Exploration and evaluation assets expenditure</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NL.xlsx
+++ b/output/pdf_financials_xlsx/NL.xlsx
@@ -1029,19 +1029,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.097151</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.022513</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00191</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.010768</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004055</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1071,13 +1071,13 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.019086</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.029263</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.018377</v>
       </c>
     </row>
     <row r="13">
@@ -1975,19 +1975,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.59981</v>
+        <v>-3.696961</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.034462</v>
+        <v>-2.056975</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.270828</v>
+        <v>-0.272738</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.356108</v>
+        <v>-5.366876</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.226747</v>
+        <v>-2.230802</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.277568</v>
@@ -1999,7 +1999,7 @@
         <v>-1.050573</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.416823</v>
+        <v>-0.416853</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.450478</v>
@@ -2017,13 +2017,13 @@
         <v>-0.218892</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.54108</v>
+        <v>-0.5601660000000001</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.087228</v>
+        <v>-0.116491</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.091751</v>
+        <v>-0.110128</v>
       </c>
     </row>
     <row r="28">
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.59981</v>
+        <v>-3.696961</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.034462</v>
+        <v>-2.056975</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.266168</v>
+        <v>-0.268078</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.351604</v>
+        <v>-5.362372</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.223482</v>
+        <v>-2.227537</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.275282</v>
@@ -2115,7 +2115,7 @@
         <v>-1.049453</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.416038</v>
+        <v>-0.416068</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.44993</v>
@@ -2133,13 +2133,13 @@
         <v>-0.2188</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.5410160000000001</v>
+        <v>-0.560102</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.087182</v>
+        <v>-0.116445</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.09171899999999999</v>
+        <v>-0.110096</v>
       </c>
     </row>
     <row r="30">
@@ -2413,40 +2413,40 @@
         <v>0.154302</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.176022</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.120416</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.186431</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.519188</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.305797</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.175321</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.072071</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.064927</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.808328</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.055699</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.059453</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.010952</v>
       </c>
     </row>
     <row r="35">
@@ -2529,40 +2529,40 @@
         <v>0.242138</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.058557</v>
+        <v>0.234579</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.00732</v>
+        <v>0.127736</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.00976</v>
+        <v>0.196191</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.041478</v>
+        <v>0.560666</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.065877</v>
+        <v>0.371674</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.175321</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.072071</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.064927</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.808328</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.055699</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.059453</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.010952</v>
       </c>
     </row>
     <row r="37">
@@ -3225,40 +3225,40 @@
         <v>0.009235</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.184736</v>
+        <v>0.008714</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.129081</v>
+        <v>0.008665000000000001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.19486</v>
+        <v>0.008429000000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.521221</v>
+        <v>0.002033</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.30795</v>
+        <v>0.002153</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.177474</v>
+        <v>0.002153</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.074091</v>
+        <v>0.00202</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.006351</v>
+        <v>0.941424</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.81111</v>
+        <v>0.002782</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.708495</v>
+        <v>0.652796</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.662235</v>
+        <v>0.602782</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.588105</v>
+        <v>0.577153</v>
       </c>
     </row>
     <row r="49">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -32411,7 +32411,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -34937,7 +34937,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -35343,7 +35343,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E274" s="5" t="n">

--- a/output/pdf_financials_xlsx/NL.xlsx
+++ b/output/pdf_financials_xlsx/NL.xlsx
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00588</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004515</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -7169,13 +7169,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>1.081146</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>1.320648</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.095774</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -7199,7 +7199,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.09907000000000001</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -8319,7 +8319,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00588</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -8328,7 +8328,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004515</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.72932</v>
+        <v>-0.7352</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.384105</v>
@@ -8386,7 +8386,7 @@
         <v>-0.52957</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.6917990000000001</v>
+        <v>-0.696314</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.656299</v>
@@ -22107,7 +22107,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E140" s="5" t="n">
         <v>1.081146</v>
       </c>
@@ -23212,7 +23216,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -28382,7 +28390,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E203" s="5" t="n">
         <v>-0.00588</v>
       </c>
